--- a/www/download/COUNTRY.ZAF.EXI382.xlsx
+++ b/www/download/COUNTRY.ZAF.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Africa do Sul</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15383435582822</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.15345705521472</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>15.167</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>13.026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>13.272</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>13.128</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>12.751</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>12.532</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11.444</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>11.138</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>11.225</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>11.388</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>11.617</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>12.272</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>12.768</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>13.184</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>13.71</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>13.303</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>13.253</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>13.202</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>13.475</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>11.648</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>11.297</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>12.588</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>11.814</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12.881</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>13.23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13.319</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>13.424</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>10.928</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>9.717</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>9.865</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>9.728</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>9.356</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>9.155</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>8.257</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>7.927</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>8.067</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>8.083</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>8.164</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>8.437</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>8.822</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>9.201</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>9.316</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>8.976</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>8.781</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>9.006</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>9.101</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>7.945</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>7.789</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8.721</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>8.378</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>8.96</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>9.272</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>9.359</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>33652.466</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>29218.244</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>29701.059</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>29378.636</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>28529.224</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>28109.956</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25779.222</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>24960.842</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>25137.543</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>25471.69</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>25957.904</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>27523.023</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>28606.862</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>29440.57</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>30626.083</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>29659.855</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>29497.125</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>29484.885</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>30095.401</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>25960.275</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>25159.391</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>28042.941</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>26265.477</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>28812.599</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>29498.321</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>29663.308</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>29877.761</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23872.981</t>
+          <t>34028975454.2669</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14035.335</t>
+          <t>36475995387.4522</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14085.217</t>
+          <t>36499534010.9391</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13791.339</t>
+          <t>38469788761.8986</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12943.436</t>
+          <t>35394155260.0943</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12559.308</t>
+          <t>37506323682.5178</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10851.051</t>
+          <t>32263092659.7961</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10164.003</t>
+          <t>32376475685.514</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10622.225</t>
+          <t>33324602504.3889</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10268.204</t>
+          <t>34123893824.8471</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10076.245</t>
+          <t>33517783094.4828</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9830.157</t>
+          <t>33143167367.8312</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10422.251</t>
+          <t>31193282729.175</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>11122.51</t>
+          <t>34546531923.429</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10421.22</t>
+          <t>32950032006.6999</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>9794.63</t>
+          <t>31972109845.085</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>9035.27</t>
+          <t>32207089654.5208</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>10287.242</t>
+          <t>34130987094.6464</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>10131.916</t>
+          <t>33996127008.9787</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>17518.417</t>
+          <t>28537046646.7257</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>17149.413</t>
+          <t>26472626252.5599</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>19192.046</t>
+          <t>27610876441.1397</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>18383.125</t>
+          <t>31032136895.0378</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19794.813</t>
+          <t>30469987489.1509</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>20408.279</t>
+          <t>31352539601.1584</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20436.148</t>
+          <t>32583653771.0846</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>20533.754</t>
+          <t>31007220733.585</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12101553325.5278</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9925449996.9285</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10022429034.1676</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>9299852399.84107</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>9549076726.5594</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>9456941699.83759</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7876983177.66545</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7312611539.67779</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>9164394521.64152</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>9434066833.91857</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>9204664809.43153</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>10057644782.9567</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>8264642378.47988</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>8765563851.59653</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>8493474928.85377</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>8686964012.65989</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>8919730552.15199</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>9082668048.10892</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>9114792613.11367</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>7128771014.49158</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>7432963187.76574</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5544287496.34442</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>8198870692.05028</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9952171247.39935</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>8590621883.06423</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>8798566058.97584</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>7915067341.30282</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>23012583.2398939</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1297907463742.3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>24794581.2231271</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>28522555.1712021</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>24747448.6064336</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>21340866.2969492</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20032729.8881551</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>17758727.3966184</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>17276052.4482042</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>15221749.9140243</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>12151533.5834368</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>11294034.3669472</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>11038848.787434</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>12575788.9887211</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>10381568.0437323</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>7758654.93281257</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7130591.84649781</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7346321.94887569</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>8182760.25671536</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>9199963.6861743</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>7198317.66458086</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8146299.83302644</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>7464413.12890227</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7760015.57609369</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>8168618.7927194</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>7761817.90111668</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>7851575.26780871</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>58777.0330418012</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>132580.242969618</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>143784.021724196</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>144973.223580274</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>144460.175150271</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>165312.115253483</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>145366.678206441</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>133964.087744538</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>128304.295345234</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>122413.189974938</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>132049.846322701</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>140301.575133457</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>154382.187627526</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>162767.6158976</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>159754.546551824</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>176053.306247709</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>182103.818032067</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>211948.992371354</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>210626.5315609</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>190945.742220539</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>207547.270090426</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>204304.315490437</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>213766.818060694</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>211941.435417546</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>234621.524151133</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>226103.033825086</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>218466.20360419</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>126846.498792106</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>277183.730892006</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>302092.919871782</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>327337.163660741</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>317672.979302048</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>402398.350716503</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>347562.279266183</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>338095.773523059</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>319675.632107079</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>319891.773779574</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>336846.07055694</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>356299.320318127</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>347428.042686078</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>386627.841203767</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>369539.521875679</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>413506.798144574</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>433646.264082146</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>507232.514874998</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>493521.070329981</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>428804.478643763</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>449350.253164148</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>427179.956646196</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>507595.476222281</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>484730.415561924</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>531421.493496368</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>525393.724763318</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>490864.773975968</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.972720410405786</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.414075388454964</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.405369603713727</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.48296317049474</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.355464651780949</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.328051731588985</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.377564272418161</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.389927883472975</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.1590754386366</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0884175510690937</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0946890091713666</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.0226183473234848</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.261065009555723</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.268886979583716</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.226967789661881</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.127508992292655</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0129532307255393</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.132623320098089</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.111590355377275</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.45742453442634</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.30721074595426</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2.46158929796744</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.24215329560972</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.988994363993556</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.3756462787234</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.32266804726879</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.59426148269715</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1107.41339711309</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1021.47311840642</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1015.98923780366</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>955.988116759884</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1020.6475835098</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1032.93593942784</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>953.953298656589</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>922.447654927858</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1135.97869470234</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1167.17806130546</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1127.53902240836</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1192.07367258367</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>936.864330561537</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>952.716545833465</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>911.727916964347</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>967.788239063896</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1015.75267635587</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1008.52419503977</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1001.50450089727</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>897.312147988336</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>954.34387361288</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>635.759756786496</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>978.567111190301</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1110.73181149116</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>926.466732875506</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>946.098645600686</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>845.707466650142</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>2353247779.72535</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-2226322021.22951</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>-709055803.969535</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-1212273021.58897</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-98197080.8007124</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>609442513.398925</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>722570520.353865</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1239308743.194</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1221568070.10968</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>2335011012.84247</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>2625086238.01644</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>2854771782.83522</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1296919135.03967</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1616384127.58431</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>2378516276.96249</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>3919054996.41891</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>4958075314.27172</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>4954024878.53295</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>4355038383.24739</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>2848182061.58489</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>2541740917.61591</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>2507254261.36796</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>4953695728.1176</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>5816664088.43892</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>4891275372.61628</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>5846653684.89188</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>4810817811.21322</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5432498317.99787</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-112756379.592491</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1368562259.33752</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>761312203.479637</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1788997741.19202</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2682694698.94297</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2539551592.06086</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2983315682.53902</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>3066279845.55079</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4690635667.96103</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5258117933.02008</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5720649054.64538</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>3725487820.8394</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>4297755536.98717</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4473538026.01706</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>6166213520.71822</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>6498169575.33168</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>6619358873.00417</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>6258578263.24051</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>4654383926.588</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>4628615363.42599</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>4559133782.23047</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>5337843766.51048</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>6336074023.36938</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>5371001758.39301</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>6373404077.63207</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>6380465054.11114</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-3079250538.27252</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-2113565641.63702</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-2077618063.30706</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-1973585225.0686</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-1887194821.99273</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-2073252185.54404</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1816981071.70699</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-1744006939.34502</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-1844711775.44111</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-2355624655.11856</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-2633031695.00364</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-2865877271.81016</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-2428568685.79974</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-2681371409.40286</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-2095021749.05457</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-2247158524.29931</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-1540094261.05997</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-1665333994.47123</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-1903539879.99312</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-1806201865.00311</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-2086874445.81008</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-2051879520.86252</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-384148038.39288</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-519409934.930465</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-479726385.776723</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-526750392.740186</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-1569647242.89793</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>2184.6170112418</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>1444.43999670686</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>1427.84039250954</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>1417.69516858553</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1383.45172137317</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>1371.79236297764</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>1314.13198178477</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1282.13571662849</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>1316.68500384395</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>1270.37708714766</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1234.30457524226</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>1165.110936222</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>1181.446825972</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>1208.88962024206</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>1118.66078705078</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>1091.18994217962</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>1028.9099551328</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1142.27802218519</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>1113.26274406434</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>2205.07688750533</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>2201.87244053525</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>2200.73917017051</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>2194.09747333061</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2209.23931296426</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>2200.95724631672</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>2197.47309370099</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2193.98630635984</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>2218.7565920424</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>2243.00218018849</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2237.92426290451</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>2237.92894664655</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>2237.46338318687</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>2243.1437290033</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>2252.66054754021</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2241.07254329786</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>2239.44472378408</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>2236.69360121521</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>2234.47572006487</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>2242.73134345375</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>2240.52995715821</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>2233.05291262123</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>2233.84998395361</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>2229.54462944731</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>2225.76138418132</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>2233.29731866954</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>2233.39178045633</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>2228.68062343111</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>2227.05255292845</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>2227.72046231633</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>2223.2642948085</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>2236.84863559087</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>2229.6341712928</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>2227.07789149961</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>2225.67806401054</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>23761.0118256436</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>27338.7316685162</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>32060.804841711</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>29549.7532823794</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>31251.5344620224</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>41563.127114066</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>43121.5467051594</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>41301.6193610422</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>40185.2951713356</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>46022.2560032451</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>52859.1262133618</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>60640.1223341607</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>56430.5553188292</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>58351.1465581401</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>52240.2095177888</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>76106.6302936097</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>87708.2414754769</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>88258.3682950898</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>81893.7067314563</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>81247.5203228283</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>87476.384706116</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>82917.7010732371</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>101873.741115869</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>104418.056901525</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>104920.773195917</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>108682.019292778</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>108738.438807854</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2141029041.4121</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4244072312.50143</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4662092685.12758</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4771431584.44413</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4249948297.32642</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4830379784.30252</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4980045217.53579</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4728042229.58256</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>3784982000.38081</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>3927525102.53402</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3803137686.50259</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>4145206474.06621</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3456103056.98624</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>4586644714.1096</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3606724336.05807</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3752757439.35286</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4172392317.93082</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>4174726206.63847</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>4095905728.80738</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>3846278325.60133</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>3336052769.56399</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>3590437021.62488</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>5382435424.19861</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>5434006328.24213</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>5515028658.14968</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>5710917143.88287</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>5185755528.3921</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>22558.0534552315</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>24872.7562837991</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>29858.0146060098</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>27562.5616483983</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>26800.1607402911</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>35691.6698943591</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35808.8207637116</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>35111.5139538135</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>35341.7222767921</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>46370.2815651845</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>53555.7573803092</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>65610.6362291187</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>60287.1705485527</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>62475.5391253209</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>51120.230330936</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>71509.0920059122</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>84540.4381561073</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>94132.2712174033</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>90194.7479388292</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>86428.3608717346</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>92392.2501761933</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>81079.6499032872</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>96701.8713646096</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>103009.312376922</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>102847.07301472</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>106722.750328119</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>106843.056117013</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>33652.466</t>
+          <t>3812769339.0342</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29218.244</t>
+          <t>1516816863.18995</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29701.059</t>
+          <t>3540701605.49614</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>29378.636</t>
+          <t>3184774996.44879</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>28529.224</t>
+          <t>3335173892.4532</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>28109.956</t>
+          <t>4528921028.69696</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25779.222</t>
+          <t>4523226694.45007</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>24960.842</t>
+          <t>4931538655.48023</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25137.543</t>
+          <t>4183735255.20387</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25471.69</t>
+          <t>6326360468.07059</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>25957.904</t>
+          <t>6544735894.24421</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>27523.023</t>
+          <t>7739549467.18832</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>28606.862</t>
+          <t>5231945942.6256</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>29440.57</t>
+          <t>6768232915.96505</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>30626.083</t>
+          <t>5820389297.35454</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>29659.855</t>
+          <t>7104926694.49258</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>29497.125</t>
+          <t>8765169999.76547</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>29484.885</t>
+          <t>9769189954.76674</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>30095.401</t>
+          <t>9401857907.56969</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>25960.275</t>
+          <t>7245215302.02129</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>25159.391</t>
+          <t>6352985249.66591</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>28042.941</t>
+          <t>5902753950.74543</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>26265.477</t>
+          <t>9837962398.91076</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>28812.599</t>
+          <t>11110655712.3334</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>29498.321</t>
+          <t>10217042794.204</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>29663.308</t>
+          <t>11367440769.6167</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>29877.761</t>
+          <t>9811896586.89149</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23872.981</t>
+          <t>1202.95837041206</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>14035.335</t>
+          <t>2465.97538471718</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14085.217</t>
+          <t>2202.79023570123</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13791.339</t>
+          <t>1987.19163398113</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12943.436</t>
+          <t>4451.37372173134</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12559.308</t>
+          <t>5871.4572197069</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10851.051</t>
+          <t>7312.72594144788</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10164.003</t>
+          <t>6190.10540722866</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10622.225</t>
+          <t>4843.57289454348</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10268.204</t>
+          <t>-348.025561939357</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10076.245</t>
+          <t>-696.631166947341</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9830.157</t>
+          <t>-4970.51389495803</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10422.251</t>
+          <t>-3856.61522972356</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>11122.51</t>
+          <t>-4124.39256718079</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>10421.22</t>
+          <t>1119.97918685289</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>9794.63</t>
+          <t>4597.53828769751</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>9035.27</t>
+          <t>3167.80331936963</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>10287.242</t>
+          <t>-5873.90292231345</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>10131.916</t>
+          <t>-8301.04120737285</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>17518.417</t>
+          <t>-5180.84054890631</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>17149.413</t>
+          <t>-4915.86547007726</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>19192.046</t>
+          <t>1838.05116994997</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>18383.125</t>
+          <t>5171.86975125906</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19794.813</t>
+          <t>1408.74452460313</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>20408.279</t>
+          <t>2073.70018119703</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20436.148</t>
+          <t>1959.26896465908</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>20533.754</t>
+          <t>1895.38269084193</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26975.427</t>
+          <t>-1671740297.6221</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29662.024</t>
+          <t>2727255449.31148</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29561.591</t>
+          <t>1121391079.63144</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>30713.1</t>
+          <t>1586656587.99533</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>28285.844</t>
+          <t>914774404.873222</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>29679.038</t>
+          <t>301458755.60556</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25458.704</t>
+          <t>456818523.085722</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>25126.719</t>
+          <t>-203496425.897675</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26134.65</t>
+          <t>-398753254.823056</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>26545.02</t>
+          <t>-2398835365.53657</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>26117.113</t>
+          <t>-2741598207.74162</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>25788.819</t>
+          <t>-3594342993.12211</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>24716.476</t>
+          <t>-1775842885.63937</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>27166.542</t>
+          <t>-2181588201.85545</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>25873.804</t>
+          <t>-2213664961.29648</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>25068.454</t>
+          <t>-3352169255.13971</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>25199.907</t>
+          <t>-4592777681.83465</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>26702.231</t>
+          <t>-5594463748.12828</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>26663.463</t>
+          <t>-5305952178.7623</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>22503.311</t>
+          <t>-3398936976.41997</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>21000.491</t>
+          <t>-3016932480.10192</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>21977.135</t>
+          <t>-2312316929.12055</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>24497.328</t>
+          <t>-4455526974.71215</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>24240</t>
+          <t>-5676649384.09129</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>24945.516</t>
+          <t>-4702014136.05436</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>25757.398</t>
+          <t>-5656523625.73379</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>24544.583</t>
+          <t>-4626141058.4994</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>42065.8888582868</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>36999.8585233804</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>43256.0716908533</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>38674.4403892872</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>39233.4218762082</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>44646.0266713949</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>39350.8027000056</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>34873.6851786188</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>42591.1239784131</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>50230.4016729527</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>55958.3381654639</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>55642.239431182</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>54134.8386755431</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>47728.5407024311</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>47551.797920664</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>59677.0933722308</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>61286.8917466475</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>57836.9752339799</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>52507.3466587714</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>45959.08009209</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>47211.8324249102</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>43938.4461595733</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>50222.8630257711</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>50651.5787222113</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>50648.8305003019</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>50370.6494010686</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>50014.0455205268</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>15768.052</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>17446.898</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>17372.303</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>17037.752</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>16095.312</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>15408.238</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>13493.923</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>12828.569</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>13375.088</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>13058.212</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>13139.587</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>13050.933</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>13860.963</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>14543.848</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>14244.532</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>13612.341</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>13524.927</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>14261.76</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>14508.978</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>12707.488</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>12227.258</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>13205.257</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>13068.755</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13322.566</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>13842.083</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14022.366</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>13800.195</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>75973.5802921815</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>74985.5158153862</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>82696.4908532834</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>74197.7074195594</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>78680.514121566</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>87935.3673307417</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>76720.1806726104</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>67583.6415879926</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>90023.7024499083</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>104921.645178953</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114806.862372878</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>118093.469882367</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>114239.569961311</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>100351.57521963</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>105251.120070298</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>138089.638278901</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>139136.552258574</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>139606.380145267</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>121294.546635586</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>110598.201132129</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>115650.888230701</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>95653.3980989815</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>119339.240032963</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>122175.340546304</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>123918.699781616</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>125717.674148669</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>126382.581345263</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>11288.611</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>9360.095</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>9393.077</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>8643.561</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>8902.037</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>8726.453</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7292.07</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>6750.388</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>8496.254</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>8686.294</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>8496.007</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>9253.328</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>7760.37</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>8208.451</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>7912.56</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>8122.48</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>8335.062</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>8483.714</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>8539.565</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>6703.745</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>6977.931</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>5214.771</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>7826.864</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>9560.451</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>8275.461</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>8448.502</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>7497.778</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>111.48</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>43.92</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>48.81</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>50.57</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>18.21</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>6.23</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>20.59</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>21.26</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>161.32</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>145.77</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>268.03</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>134.87</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>146.61</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>141.89</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>173.86</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>24.337</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1532826.247</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>26.874</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>30.751</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>26.643</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>22.632</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>21.359</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>18.291</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>12.589</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>11.638</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>11.683</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>13.104</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>10.637</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>7.975</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>7.27</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>7.473</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>8.41</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>9.569</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>7.58</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>8.556</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>7.777</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>8.179</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>8.659</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>8.134</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>8.232</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>53921.2527118452</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>52656.7919621888</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>64453.6396020207</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>60137.5794390202</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>60796.0070041708</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>71710.1660803348</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>70498.0920939978</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>61090.7507524745</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>74217.4720446216</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>88874.2511670938</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>103641.858368839</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>110131.381509844</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>115578.7277942</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>103083.541026708</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>115569.886374587</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>155472.424318778</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>168682.20655595</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>176362.734383508</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>158522.442061619</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>155658.866478302</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>171467.421916856</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>169340.843847436</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>186520.747410983</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>186672.948975235</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>186679.076626578</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>188872.552657242</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>193434.797737459</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>23872981242.8827</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>14035334559.997</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>14085217119.9971</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>13791338600.0014</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>12943435959.9954</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>12559307800.0054</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10851050599.9908</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>10164002680.0044</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>10622224600.0105</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>10268203919.9958</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10076245399.9911</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>9830157479.99958</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>10422251319.9924</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>11122509840.0005</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>10421220160.0043</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>9794630039.99671</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>9035269880.00366</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>10287241639.998</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>10131915560.0012</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>17518416791.3189</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>17149412541.0955</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>19192046262.2005</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>18383124942.4585</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>19794812520.576</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>20408278908.4213</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20436148246.9668</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20533754336.496</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>33652466485.8443</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>29218243600.0016</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>29701059440.0019</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>29378636039.9991</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>28529224360.0008</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>28109955640.0057</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25779222039.9914</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>24960841880.0017</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>25137543080.0039</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>25471690399.9989</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>25957904439.9961</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>27523023319.9992</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>28606862439.996</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>29440569599.9998</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>30626083280</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>29659855159.9964</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>29497125320.0028</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>29484884520.002</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>30095400920.0011</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>25960275242.1191</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>25159391037.1464</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>28042941303.7798</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>26265477091.8502</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>28812598727.8432</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>29498320775.3631</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>29663307556.8325</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>29877760858.5723</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>15768052202.4669</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>17446898183.614</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>17372303175.3916</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>17037751610.278</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>16095312479.528</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>15408238359.5727</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13493922926.6283</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>12828569208.0599</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>13375087784.4623</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>13058212307.5912</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>13139586575.5124</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>13050933081.9567</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>13860962948.7082</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>14543848216.4127</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>14244531668.4403</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>13612341250.9754</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>13524926834.5554</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>14261759865.9517</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>14508977932.0209</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>12707487501.0064</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>12227257628.4404</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>13205257230.9009</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>13068755480.3407</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13322565859.8688</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>13842083388.1512</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14022365748.7864</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>13800195404.356</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>15167263.775819</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13026399.9999975</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13271700.0000054</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>13127600.0000008</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>12750700</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>12531500.0000004</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>11443899.9999982</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>11137900.000002</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>11224900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>11388100</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>11617000.0000011</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>12272100.0000002</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>12767899.9999981</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>13184000.0000007</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>13709999.9999982</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>13303099.9999981</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>13252600.0000006</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>13202399.9999997</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>13475199.9999982</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>11648270.7163993</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>11297169.886747</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>12588177.8159103</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>11813924.7561265</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12880888.8851043</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>13230116.9201489</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13319384.8630318</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>13424116.1566441</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10927764.9675137</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>9716799.99999709</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>9864700.00000575</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>9728000.00000096</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>9355900.00000008</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9155399.99999993</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8257199.99999817</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>7927400.00000291</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>8067399.99999988</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>8082799.99999896</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>8163500.00000077</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>8437100.00000084</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>8821599.9999981</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>9200600.0000012</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>9315799.99999704</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>8976099.99999841</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>8781400.0000005</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>9005900.00000027</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>9101099.99999749</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>7944583.19824758</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>7788558.60375214</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>8720727.34576425</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>8378444.97152311</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>8960012.79916397</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>9272455.85645717</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>9299840.03242024</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>9359107.79250242</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>33652466485.8443</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>29218243600.0016</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>29701059440.0019</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>29378636039.9991</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>28529224360.0008</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>28109955640.0057</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>25779222039.9914</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>24960841880.0017</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>25137543080.0039</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>25471690399.9989</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>25957904439.9961</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>27523023319.9992</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>28606862439.996</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>29440569599.9998</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>30626083280</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>29659855159.9964</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>29497125320.0028</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>29484884520.002</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>30095400920.0011</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>25960275242.1191</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>25159391037.1464</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>28042941303.7798</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>26265477091.8502</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>28812598727.8432</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>29498320775.3631</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>29663307556.8325</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>29877760858.5723</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>23872981242.8827</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>14035334559.997</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>14085217119.9971</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13791338600.0014</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>12943435959.9954</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>12559307800.0054</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10851050599.9908</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>10164002680.0044</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>10622224600.0105</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>10268203919.9958</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>10076245399.9911</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>9830157479.99958</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>10422251319.9924</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>11122509840.0005</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>10421220160.0043</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>9794630039.99671</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>9035269880.00366</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>10287241639.998</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>10131915560.0012</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>17518416791.3189</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>17149412541.0955</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>19192046262.2005</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>18383124942.4585</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>19794812520.576</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>20408278908.4213</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>20436148246.9668</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>20533754336.496</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>255167.073421807</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>247480.879398336</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>288767.90786975</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>265623.946377856</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>285461.310553646</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>338325.191840369</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>317136.786601553</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>297720.393704264</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>384949.589290828</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>457312.466617661</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>513167.616558645</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>539092.774852317</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>534889.220571794</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>494398.675146216</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>532209.393377847</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>697241.617981521</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>741655.289446011</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>774457.124446553</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>682833.969811149</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>645860.730287133</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>713434.554274471</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>653778.197231217</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>758155.38577081</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>762689.738676672</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>774819.222662216</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>779969.829982085</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>797115.653464984</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>83182.8012200634</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>81600.3425586891</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>91120.6972249038</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>81865.8944252988</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>87263.2639763285</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>98770.839307522</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>86372.129479571</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>78242.3404691636</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>101981.128813166</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>120100.327695967</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>131915.443354196</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>135693.864856191</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>132697.820504332</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>118586.389996473</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>125523.65316716</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>166231.853252965</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>171135.166183607</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>173892.369476723</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>154984.100965135</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>143985.59115563</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>153259.421336253</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>134654.476666987</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>164239.730173721</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>167163.136964405</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>169674.153665629</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>171259.736820849</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>171948.939648722</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3609,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3673,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4034,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
